--- a/05_mega_project_5_liquidity_cashflow/decision_engine/reports/notebook_05_workbook.xlsx
+++ b/05_mega_project_5_liquidity_cashflow/decision_engine/reports/notebook_05_workbook.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>90-day stressed collections range from $14,860,661,28 ($1.49B)6 (Baseline) to $12,817,989,83 ($1.28B)2 (Severely Adverse).</t>
+          <t>90-day stressed collections range from $14,860,661,286 ($14.86B) (Baseline) to $12,817,989,832 ($12.82B) (Severely Adverse).</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -935,12 +935,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
